--- a/data/trans_orig/IP3103-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3103-Estudios-trans_orig.xlsx
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37645</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>36427</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51443</t>
+          <t>51244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34786</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>48489</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>74643</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96111</t>
+          <t>95652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34841</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39601</t>
+          <t>39217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58666</t>
+          <t>58877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>39531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>27996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45982</t>
+          <t>47058</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54792</t>
+          <t>54096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80290</t>
+          <t>79248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>165899</t>
+          <t>167545</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>197864</t>
+          <t>198408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>202121</t>
+          <t>199950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>234749</t>
+          <t>232711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>377569</t>
+          <t>376992</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>423227</t>
+          <t>422472</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,27%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140456</t>
+          <t>138995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169921</t>
+          <t>169795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155334</t>
+          <t>156758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188495</t>
+          <t>189978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>305579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348386</t>
+          <t>350522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27167</t>
+          <t>28970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>28667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>51240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>26339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>38595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65509</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86014</t>
+          <t>85121</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63835</t>
+          <t>63754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82616</t>
+          <t>83087</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>135894</t>
+          <t>135339</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>163862</t>
+          <t>162943</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51322</t>
+          <t>50739</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70566</t>
+          <t>70400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44487</t>
+          <t>42744</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>61365</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99399</t>
+          <t>99782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126111</t>
+          <t>126480</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>53326</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78316</t>
+          <t>77989</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50217</t>
+          <t>48667</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73907</t>
+          <t>73095</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>108195</t>
+          <t>108332</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>143610</t>
+          <t>143642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281962</t>
+          <t>282065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>323639</t>
+          <t>324004</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>311726</t>
+          <t>312800</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>355538</t>
+          <t>354548</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>606442</t>
+          <t>606789</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>666715</t>
+          <t>664430</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>222073</t>
+          <t>221236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>261997</t>
+          <t>262685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224171</t>
+          <t>227581</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266307</t>
+          <t>265260</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>461145</t>
+          <t>461799</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>517665</t>
+          <t>515263</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38241</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42431</t>
+          <t>43227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64862</t>
+          <t>66858</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>17289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>31136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>37963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58583</t>
+          <t>58169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>45860</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48840</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68433</t>
+          <t>67704</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89291</t>
+          <t>90500</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38071</t>
+          <t>38653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>46892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70851</t>
+          <t>70715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54902</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79221</t>
+          <t>76495</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107429</t>
+          <t>107079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141405</t>
+          <t>140602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174424</t>
+          <t>173520</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>206088</t>
+          <t>207077</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183898</t>
+          <t>184508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>219009</t>
+          <t>220817</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>370814</t>
+          <t>370796</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>417772</t>
+          <t>417449</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108333</t>
+          <t>106629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138222</t>
+          <t>136873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117481</t>
+          <t>118027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151184</t>
+          <t>149722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233921</t>
+          <t>233917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277938</t>
+          <t>279137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38294</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61949</t>
+          <t>60381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76117</t>
+          <t>77488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104971</t>
+          <t>104859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25805</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45298</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63561</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83317</t>
+          <t>84283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56219</t>
+          <t>55881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77054</t>
+          <t>76377</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125524</t>
+          <t>126350</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>153519</t>
+          <t>153424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33680</t>
+          <t>33498</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51309</t>
+          <t>52087</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60532</t>
+          <t>61054</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79871</t>
+          <t>80653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106372</t>
+          <t>107114</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29923</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48953</t>
+          <t>49775</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>83499</t>
+          <t>84233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114339</t>
+          <t>115132</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>92083</t>
+          <t>91172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>123464</t>
+          <t>124709</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>182855</t>
+          <t>185284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>226484</t>
+          <t>228324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282638</t>
+          <t>281009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>324864</t>
+          <t>323176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>287489</t>
+          <t>288523</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>330719</t>
+          <t>331276</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>581048</t>
+          <t>578280</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>640469</t>
+          <t>641407</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>162222</t>
+          <t>160986</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>200140</t>
+          <t>199349</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177617</t>
+          <t>176994</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>217967</t>
+          <t>216142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>351475</t>
+          <t>351902</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>405807</t>
+          <t>406560</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>55659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80212</t>
+          <t>81283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61458</t>
+          <t>61475</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86856</t>
+          <t>86850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>122803</t>
+          <t>123882</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159493</t>
+          <t>161454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>24834</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12165</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22744</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39666</t>
+          <t>39703</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23791</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40372</t>
+          <t>38637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>22307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34888</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>35949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52692</t>
+          <t>53670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41258</t>
+          <t>41522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>64185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80138</t>
+          <t>80373</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111179</t>
+          <t>112159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142291</t>
+          <t>142569</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174721</t>
+          <t>175810</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150672</t>
+          <t>151595</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184622</t>
+          <t>185134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>306093</t>
+          <t>303402</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>351807</t>
+          <t>353836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98505</t>
+          <t>99224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127709</t>
+          <t>126824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115321</t>
+          <t>115626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147041</t>
+          <t>147045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222922</t>
+          <t>221613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>264361</t>
+          <t>265497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100709</t>
+          <t>99175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130979</t>
+          <t>130484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99614</t>
+          <t>98940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130129</t>
+          <t>129732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207122</t>
+          <t>208797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250510</t>
+          <t>250031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>24277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>24880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42690</t>
+          <t>42691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58373</t>
+          <t>57704</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78331</t>
+          <t>78115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>55854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75885</t>
+          <t>76509</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118498</t>
+          <t>118937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>147776</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,35%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>35303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53387</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39983</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59119</t>
+          <t>59926</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80326</t>
+          <t>78909</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106675</t>
+          <t>105778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22075</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>37519</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29043</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45618</t>
+          <t>46398</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54946</t>
+          <t>55855</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79667</t>
+          <t>78836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61481</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88394</t>
+          <t>88853</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>58825</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87397</t>
+          <t>86912</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>128712</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>166873</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>223376</t>
+          <t>221770</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>264388</t>
+          <t>263654</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>228659</t>
+          <t>228204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>270044</t>
+          <t>271364</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>464806</t>
+          <t>464451</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>522829</t>
+          <t>523166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>154788</t>
+          <t>155368</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>193295</t>
+          <t>194104</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172585</t>
+          <t>173055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>211685</t>
+          <t>209678</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>338515</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>393568</t>
+          <t>393357</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143423</t>
+          <t>142833</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>178662</t>
+          <t>178026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>161860</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>198444</t>
+          <t>199892</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>313279</t>
+          <t>315970</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>365024</t>
+          <t>367613</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3103-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3103-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14313</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9191</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20762</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14910</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10060</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21754</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10179</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21116</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,03%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14313</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9392</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20226</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>37057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>41727</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34467</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48940</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>51,21%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>42,3%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>60,06%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>43714</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36427</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51244</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36423</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>51547</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>50,29%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>41,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>58,96%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>41727</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34224</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>48489</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>51,21%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74643</t>
+          <t>74538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95652</t>
+          <t>96502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21280</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15385</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27870</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>27679</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20890</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>35651</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20940</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>35060</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>31,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21280</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15399</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27808</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>26,12%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39217</t>
+          <t>39591</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58877</t>
+          <t>58620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4163</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8269</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>616</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3082</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4163</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8950</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>81483</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>81483</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>81483</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>86919</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>86919</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>86919</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>81483</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>81483</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>81483</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,107 +1404,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3930</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8002</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1867</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5028</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3930</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1372</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7943</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>5797</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>10038</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>3137</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>10406</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35998</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27580</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46240</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>30222</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22973</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>39531</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22430</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>39833</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35998</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27996</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>47058</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54096</t>
+          <t>53949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79248</t>
+          <t>79046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>217275</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200406</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>234699</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>48,27%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>44,52%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>52,14%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>183253</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>167545</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>198408</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>168136</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>199434</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>46,96%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>50,84%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>217275</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>199950</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>232711</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>48,27%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>376992</t>
+          <t>378735</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>422472</t>
+          <t>423739</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>172699</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>158182</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>191326</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>154586</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>138995</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>169795</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>139161</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>169843</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>39,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>172699</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>156758</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>189978</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305579</t>
+          <t>302607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>350522</t>
+          <t>349606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20227</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14125</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28342</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20335</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14361</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28970</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13531</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27136</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>20227</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14089</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28667</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51240</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>450128</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>450128</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>450128</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>588</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>390264</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>390264</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>390264</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>450128</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>450128</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>450128</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4826</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>448</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2269</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2587</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1471</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5063</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10462</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5861</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>16199</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19036</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13016</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26339</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12826</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>27530</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,88%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>10462</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>6193</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>16250</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21499</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38595</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -2317,67 +2317,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>73779</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>64117</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>84184</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>51,89%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>45,1%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>59,21%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>75444</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>66094</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>85121</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>64592</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>85725</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>47,1%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>41,26%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73779</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>63754</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>83087</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>135339</t>
+          <t>133789</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162943</t>
+          <t>163504</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>52527</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42603</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>61925</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>36,95%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>60706</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>50739</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>70400</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>51415</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>70747</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>37,9%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>31,68%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>52527</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>42744</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>61365</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>36,95%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99782</t>
+          <t>98527</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126480</t>
+          <t>126727</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3932</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7991</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>4543</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1772</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8987</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9465</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,84%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3932</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7804</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>142171</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>142171</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>142171</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>160176</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>160176</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>160176</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>142171</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>142171</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>142171</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5401</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10480</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2315</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5577</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5401</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>9994</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>60773</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>49507</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>73443</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>64168</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>53326</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>77989</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>53348</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>77328</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>60773</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>48667</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>73095</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>108332</t>
+          <t>109151</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>143642</t>
+          <t>141822</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>332781</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>312140</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>351209</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>49,39%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>46,33%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>52,12%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>453</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>302411</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>282065</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>324004</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>283658</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>323305</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>47,45%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>50,84%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>332781</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>312800</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>354548</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>49,39%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>606789</t>
+          <t>606772</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>664430</t>
+          <t>665297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>246505</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>226429</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>266158</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>36,59%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>33,61%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>39,5%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>242972</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>221236</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>262685</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>221947</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>260900</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>38,12%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>41,21%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>246505</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>227581</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>265260</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>36,59%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>461799</t>
+          <t>460334</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>515263</t>
+          <t>517649</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -3220,72 +3220,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>28322</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20829</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>37429</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>25494</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>18218</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>33478</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>18334</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>34610</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>28322</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>20825</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>37965</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43227</t>
+          <t>43603</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66858</t>
+          <t>65908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>673782</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>673782</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>673782</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>637360</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>637360</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>637360</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>673782</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>673782</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>673782</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,107 +3681,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1448</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5892</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -3799,67 +3799,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>23870</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17407</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30619</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>23773</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17289</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31136</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17713</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31673</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23870</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17265</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30945</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37963</t>
+          <t>37774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58169</t>
+          <t>57739</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -3912,67 +3912,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>40795</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33427</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48023</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>49,37%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>40,46%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>58,12%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>38794</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31411</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>45860</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>31050</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>45940</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>44,34%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>52,42%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40795</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>33521</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>48508</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>49,37%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67704</t>
+          <t>69050</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90500</t>
+          <t>91112</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -4020,72 +4020,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12561</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8269</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19245</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16684</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11333</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22760</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11213</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23841</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,07%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12561</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7236</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18208</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38653</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -4133,72 +4133,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5399</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10647</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6791</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12384</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12347</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>7,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5399</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2660</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9979</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>87490</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87490</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87490</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4476</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4446</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64806</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52860</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77280</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>17,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>58285</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46892</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>70715</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46911</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>71021</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>14,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>11,37%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64806</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>51731</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>14,35%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107079</t>
+          <t>106913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140602</t>
+          <t>142422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202547</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>184629</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>218910</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>44,85%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>40,88%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>48,48%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>190450</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173520</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>207077</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>173217</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>206498</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>46,18%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>50,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>202547</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>184508</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>220817</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>44,85%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>370796</t>
+          <t>369093</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>417449</t>
+          <t>415877</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,13%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>133199</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>118151</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>149758</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>121506</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>106629</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>136873</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>107366</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>137259</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>29,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>133199</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>118027</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>149722</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233917</t>
+          <t>232189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279137</t>
+          <t>275962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49098</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38624</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>61533</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>40928</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>31033</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51915</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>31799</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>52395</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>9,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>49098</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>38015</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>60381</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77488</t>
+          <t>76060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104859</t>
+          <t>105210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>451589</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>451589</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>451589</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>597</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>412434</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>412434</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>412434</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>451589</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>451589</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>451589</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,107 +5045,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1467</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5029</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18241</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11996</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>25025</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16712</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11150</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24804</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>10903</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>23571</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,95%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>18241</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>11953</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>26320</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>44989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>65704</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56438</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>77274</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>42,39%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>49,86%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>73441</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63649</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>84283</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>64490</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>84690</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>48,11%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>41,7%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>55,22%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>65704</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>55881</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>76377</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>42,39%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126350</t>
+          <t>125104</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>153424</t>
+          <t>153344</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -5384,72 +5384,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>50814</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>41262</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>61148</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>32,79%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>39,45%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>42563</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>33498</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>52087</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>33710</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>52050</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>27,88%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>34,12%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>50814</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>41842</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>61054</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80653</t>
+          <t>80415</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107114</t>
+          <t>106119</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -5497,72 +5497,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18762</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12967</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>25873</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>19929</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13381</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>27686</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>14065</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>27770</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>13,06%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>18762</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>12724</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>26821</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>30073</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49775</t>
+          <t>49167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>154989</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>154989</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>154989</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>152645</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>152645</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>152645</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>154989</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>154989</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>154989</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3407</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7918</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2712</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6917</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3407</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>8159</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>106917</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>90968</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>124822</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>15,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>98770</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>84233</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>115132</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>85027</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>113754</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>15,14%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>17,64%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>106917</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>91172</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>124709</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>185284</t>
+          <t>184874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>228324</t>
+          <t>228359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>309046</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>286727</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>329667</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>44,84%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>433</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>302685</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>281009</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>323176</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>282386</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>325510</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>46,38%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>43,06%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>49,52%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>309046</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>288523</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>331276</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>44,84%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>578280</t>
+          <t>579456</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>641407</t>
+          <t>642414</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>196574</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>180346</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>218710</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>28,52%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>26,17%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>31,73%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>180753</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>160986</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>199349</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>161289</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>197723</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>27,7%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>24,67%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>30,55%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>196574</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>176994</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>216142</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>28,52%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>351902</t>
+          <t>352903</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>406560</t>
+          <t>404968</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>73259</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>61164</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>88834</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>67649</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>55659</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>81283</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>56671</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>81356</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>10,37%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>73259</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>61475</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>86850</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>123882</t>
+          <t>123709</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161454</t>
+          <t>158739</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>689203</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>689203</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>689203</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>652569</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>652569</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>652569</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>689203</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>689203</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>689203</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12011</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17804</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5569</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10289</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10460</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>9,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12011</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7180</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17672</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24834</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13769</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8794</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20795</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>17104</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12299</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22854</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11797</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>23355</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>30,46%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>40,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13769</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9007</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20195</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24016</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39703</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -6979,72 +6979,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12842</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7617</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18196</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18018</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12546</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24307</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12461</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24033</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>32,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12842</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7826</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18593</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22770</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -7092,72 +7092,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28672</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22573</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35725</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>33,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>53,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>15464</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21428</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10482</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21563</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>27,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28672</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22307</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35520</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>42,61%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>35493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>53648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67293</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67293</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67293</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>56155</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>56155</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>56155</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67293</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67293</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7327,67 +7327,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>3520</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7680</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>3487</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7702</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7331</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7374</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43322</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53650</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>51795</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41522</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>64185</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40705</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>64818</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>11,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>43322</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>54336</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80373</t>
+          <t>81295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112159</t>
+          <t>110757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -7553,67 +7553,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>169132</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>152299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186872</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>36,72%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>158330</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>142569</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>175810</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>142825</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>175571</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>35,88%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>32,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>39,84%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169132</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>151595</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>185134</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>36,72%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>303402</t>
+          <t>303438</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>353836</t>
+          <t>352074</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>130214</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>115698</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>147395</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>99224</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>126824</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>97546</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>127797</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>25,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>130214</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>115626</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>147045</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221613</t>
+          <t>221788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265497</t>
+          <t>263729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -7774,72 +7774,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>114412</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>98824</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>129602</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>115094</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>99175</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>130484</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>100329</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>130405</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,08%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>114412</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>98940</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>129732</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,84%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208797</t>
+          <t>209644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250031</t>
+          <t>251289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>460600</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>460600</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>460600</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>663</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>441304</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>441304</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>441304</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>460600</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>460600</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>460600</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8122,67 +8122,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>16385</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23627</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>16667</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10553</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24277</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11232</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24381</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>16385</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>10571</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23761</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42691</t>
+          <t>43196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>66238</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>55288</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>76606</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>32,81%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>45,46%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>67912</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>57704</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>78115</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>57425</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>79022</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>43,16%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>36,67%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>49,64%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>55854</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>76509</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>39,31%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118937</t>
+          <t>119310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>147776</t>
+          <t>147408</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -8343,72 +8343,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>40304</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>60385</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>35,84%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>43566</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>35303</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>52943</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>35414</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>52803</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>27,69%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>48942</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>39744</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>59926</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78909</t>
+          <t>79159</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105778</t>
+          <t>105725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -8456,72 +8456,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>36944</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>28596</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>45487</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>21,92%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,97%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>29215</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>21789</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>37519</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>22104</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>39292</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>18,57%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>36944</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>28917</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>46398</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>21,92%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55855</t>
+          <t>55336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78836</t>
+          <t>80110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>168509</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>168509</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>168509</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>157360</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>157360</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>157360</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>168509</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>168509</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>168509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8691,67 +8691,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>3520</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7655</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>3487</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7970</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7758</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>71718</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>59160</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>86209</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>74031</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>61699</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>88853</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>60531</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>88473</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>11,31%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>71718</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>58825</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>86912</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127575</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>165202</t>
+          <t>165369</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>249139</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>230462</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>270284</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>35,78%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>363</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>243346</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>221770</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>263654</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>224814</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>263836</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>37,16%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>33,87%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>249139</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>228204</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>271364</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>35,78%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>464451</t>
+          <t>465194</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>523166</t>
+          <t>521780</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>191998</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>172978</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>211929</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>24,84%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>30,43%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>174184</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>155368</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>194104</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>158257</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>194864</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>26,6%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>23,73%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>191998</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>173055</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>209678</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>27,57%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>340311</t>
+          <t>338682</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>393357</t>
+          <t>392083</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>180027</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>160567</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>197707</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>25,85%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>159772</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>142833</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>178026</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>143588</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>177048</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>24,4%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>27,19%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>180027</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>161860</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>199892</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>315970</t>
+          <t>313734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>367613</t>
+          <t>365736</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>696402</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>696402</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>696402</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>982</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>654820</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>654820</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>654820</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>696402</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>696402</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>696402</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
